--- a/salidas/empresas/BLK.xlsx
+++ b/salidas/empresas/BLK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -431,62 +443,62 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>81.14112091064453</v>
+        <v>81.14112854003906</v>
       </c>
       <c r="C2" t="n">
         <v>132.8000030517578</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>86.82344818115234</v>
+        <v>86.82345581054688</v>
       </c>
       <c r="C3" t="n">
         <v>142.1000061035156</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>85.79317474365234</v>
+        <v>85.793212890625</v>
       </c>
       <c r="C4" t="n">
         <v>140</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>92.86501312255859</v>
+        <v>92.86500549316406</v>
       </c>
       <c r="C5" t="n">
         <v>151.5399932861328</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>82.11635589599609</v>
+        <v>82.11634063720703</v>
       </c>
       <c r="C6" t="n">
         <v>134</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>85.54868316650391</v>
+        <v>85.54867553710938</v>
       </c>
       <c r="C7" t="n">
         <v>139.1699981689453</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>79.39548492431641</v>
+        <v>79.39546203613281</v>
       </c>
       <c r="C8" t="n">
         <v>129.1600036621094</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>80.26375579833984</v>
+        <v>80.26374053955078</v>
       </c>
       <c r="C9" t="n">
         <v>130.1499938964844</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>93.02330780029297</v>
+        <v>93.02330017089844</v>
       </c>
       <c r="C11" t="n">
         <v>150.8399963378906</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>88.67409515380859</v>
+        <v>88.67408752441406</v>
       </c>
       <c r="C12" t="n">
         <v>143.3699951171875</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>93.94986724853516</v>
+        <v>93.94990539550781</v>
       </c>
       <c r="C13" t="n">
         <v>151.8999938964844</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>103.7592849731445</v>
+        <v>103.7592315673828</v>
       </c>
       <c r="C14" t="n">
         <v>167.7599945068359</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>98.49588012695312</v>
+        <v>98.49585723876953</v>
       </c>
       <c r="C15" t="n">
         <v>159.25</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>97.0953369140625</v>
+        <v>97.09526062011719</v>
       </c>
       <c r="C16" t="n">
         <v>156.3099975585938</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>92.98932647705078</v>
+        <v>92.98934173583984</v>
       </c>
       <c r="C17" t="n">
         <v>149.6999969482422</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>95.37467193603516</v>
+        <v>95.3746337890625</v>
       </c>
       <c r="C18" t="n">
         <v>153.5399932861328</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>97.69721984863281</v>
+        <v>97.69725799560547</v>
       </c>
       <c r="C19" t="n">
         <v>156.5899963378906</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>99.51284790039062</v>
+        <v>99.51277160644531</v>
       </c>
       <c r="C20" t="n">
         <v>159.5</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>97.20078277587891</v>
+        <v>97.20075225830078</v>
       </c>
       <c r="C21" t="n">
         <v>155.1000061035156</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>108.6755523681641</v>
+        <v>108.6755905151367</v>
       </c>
       <c r="C22" t="n">
         <v>173.4100036621094</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>129.6950225830078</v>
+        <v>129.6950073242188</v>
       </c>
       <c r="C23" t="n">
         <v>206.9499969482422</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>124.7349166870117</v>
+        <v>124.7349090576172</v>
       </c>
       <c r="C24" t="n">
         <v>198.3699951171875</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>136.3236694335938</v>
+        <v>136.32373046875</v>
       </c>
       <c r="C25" t="n">
         <v>216.8000030517578</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>138.5873107910156</v>
+        <v>138.5872955322266</v>
       </c>
       <c r="C26" t="n">
         <v>220.3999938964844</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>121.5154800415039</v>
+        <v>121.5154418945312</v>
       </c>
       <c r="C27" t="n">
         <v>193.25</v>
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>127.3848419189453</v>
+        <v>127.3848571777344</v>
       </c>
       <c r="C29" t="n">
         <v>201.7899932861328</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>142.0304412841797</v>
+        <v>142.0304107666016</v>
       </c>
       <c r="C30" t="n">
         <v>224.9900054931641</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>112.1444473266602</v>
+        <v>112.1445083618164</v>
       </c>
       <c r="C31" t="n">
         <v>177</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>137.3041381835938</v>
+        <v>137.3041076660156</v>
       </c>
       <c r="C32" t="n">
         <v>216.7100067138672</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>138.1523132324219</v>
+        <v>138.1522827148438</v>
       </c>
       <c r="C33" t="n">
         <v>217.25</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>123.6852188110352</v>
+        <v>123.6852798461914</v>
       </c>
       <c r="C34" t="n">
         <v>194.5</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>83.52094268798828</v>
+        <v>83.52091979980469</v>
       </c>
       <c r="C35" t="n">
         <v>131.3399963378906</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>79.94075012207031</v>
+        <v>79.94076538085938</v>
       </c>
       <c r="C36" t="n">
         <v>125.7099990844727</v>
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>69.61942291259766</v>
+        <v>69.61939239501953</v>
       </c>
       <c r="C38" t="n">
         <v>108.8000030517578</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>61.94720077514648</v>
+        <v>61.94718170166016</v>
       </c>
       <c r="C39" t="n">
         <v>96.80999755859375</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>83.88971710205078</v>
+        <v>83.88974761962891</v>
       </c>
       <c r="C40" t="n">
         <v>130.0399932861328</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>94.52111053466797</v>
+        <v>94.5211181640625</v>
       </c>
       <c r="C41" t="n">
         <v>146.5200042724609</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>102.8946075439453</v>
+        <v>102.8946228027344</v>
       </c>
       <c r="C42" t="n">
         <v>159.5</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>113.7037811279297</v>
+        <v>113.703742980957</v>
       </c>
       <c r="C43" t="n">
         <v>175.4199981689453</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>123.5041961669922</v>
+        <v>123.5042495727539</v>
       </c>
       <c r="C44" t="n">
         <v>190.5399932861328</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>129.8598175048828</v>
+        <v>129.8598785400391</v>
       </c>
       <c r="C45" t="n">
         <v>199.5700073242188</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>141.0844573974609</v>
+        <v>141.0843963623047</v>
       </c>
       <c r="C46" t="n">
         <v>216.8200073242188</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>140.8696746826172</v>
+        <v>140.8696899414062</v>
       </c>
       <c r="C47" t="n">
         <v>216.4900054931641</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2669677734375</v>
+        <v>148.2669067382812</v>
       </c>
       <c r="C48" t="n">
         <v>227.0800018310547</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>151.6098785400391</v>
+        <v>151.6098937988281</v>
       </c>
       <c r="C49" t="n">
         <v>232.1999969482422</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>139.6091766357422</v>
+        <v>139.609130859375</v>
       </c>
       <c r="C50" t="n">
         <v>213.8200073242188</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>142.8606567382812</v>
+        <v>142.8606872558594</v>
       </c>
       <c r="C51" t="n">
         <v>218.8000030517578</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>142.8427124023438</v>
+        <v>142.8426818847656</v>
       </c>
       <c r="C52" t="n">
         <v>217.7599945068359</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>120.6973419189453</v>
+        <v>120.697395324707</v>
       </c>
       <c r="C53" t="n">
         <v>184</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>110.1232376098633</v>
+        <v>110.1232147216797</v>
       </c>
       <c r="C54" t="n">
         <v>167.8800048828125</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>94.63959503173828</v>
+        <v>94.63957977294922</v>
       </c>
       <c r="C55" t="n">
         <v>143.3999938964844</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>103.9385757446289</v>
+        <v>103.938606262207</v>
       </c>
       <c r="C56" t="n">
         <v>157.4900054931641</v>
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>94.34629058837891</v>
+        <v>94.34628295898438</v>
       </c>
       <c r="C57" t="n">
         <v>141.9499969482422</v>
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>113.1556701660156</v>
+        <v>113.1557006835938</v>
       </c>
       <c r="C58" t="n">
         <v>170.25</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>113.6475372314453</v>
+        <v>113.6475067138672</v>
       </c>
       <c r="C59" t="n">
         <v>170.9900054931641</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>108.3370590209961</v>
+        <v>108.3370208740234</v>
       </c>
       <c r="C60" t="n">
         <v>163</v>
@@ -1603,11 +1615,11 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>127.4497985839844</v>
+        <v>127.4498596191406</v>
       </c>
       <c r="C61" t="n">
         <v>190.5800018310547</v>
@@ -1622,7 +1634,7 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1641,7 +1653,7 @@
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1660,11 +1672,11 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>135.3608551025391</v>
+        <v>135.3608703613281</v>
       </c>
       <c r="C64" t="n">
         <v>201.0099945068359</v>
@@ -1679,7 +1691,7 @@
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1698,11 +1710,11 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>138.4248352050781</v>
+        <v>138.4247894287109</v>
       </c>
       <c r="C66" t="n">
         <v>205.5599975585938</v>
@@ -1717,11 +1729,11 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>130.0615692138672</v>
+        <v>130.0615539550781</v>
       </c>
       <c r="C67" t="n">
         <v>191.8099975585938</v>
@@ -1736,11 +1748,11 @@
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>121.0092697143555</v>
+        <v>121.0093078613281</v>
       </c>
       <c r="C68" t="n">
         <v>178.4600067138672</v>
@@ -1755,11 +1767,11 @@
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>112.6402816772461</v>
+        <v>112.6403045654297</v>
       </c>
       <c r="C69" t="n">
         <v>164.75</v>
@@ -1774,11 +1786,11 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>101.1951217651367</v>
+        <v>101.1951065063477</v>
       </c>
       <c r="C70" t="n">
         <v>148.0099945068359</v>
@@ -1793,11 +1805,11 @@
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>107.8816757202148</v>
+        <v>107.881721496582</v>
       </c>
       <c r="C71" t="n">
         <v>157.7899932861328</v>
@@ -1812,11 +1824,11 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>117.6245346069336</v>
+        <v>117.6244659423828</v>
       </c>
       <c r="C72" t="n">
         <v>172.0399932861328</v>
@@ -1831,11 +1843,11 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>122.8453063964844</v>
+        <v>122.8453140258789</v>
       </c>
       <c r="C73" t="n">
         <v>178.2400054931641</v>
@@ -1850,11 +1862,11 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>125.4367752075195</v>
+        <v>125.4367294311523</v>
       </c>
       <c r="C74" t="n">
         <v>182</v>
@@ -1869,11 +1881,11 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>137.1533050537109</v>
+        <v>137.1533508300781</v>
       </c>
       <c r="C75" t="n">
         <v>199</v>
@@ -1888,11 +1900,11 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>142.2963562011719</v>
+        <v>142.2963256835938</v>
       </c>
       <c r="C76" t="n">
         <v>204.8999938964844</v>
@@ -1907,11 +1919,11 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>133.0460357666016</v>
+        <v>133.0460510253906</v>
       </c>
       <c r="C77" t="n">
         <v>191.5800018310547</v>
@@ -1926,11 +1938,11 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>118.6150436401367</v>
+        <v>118.6150283813477</v>
       </c>
       <c r="C78" t="n">
         <v>170.8000030517578</v>
@@ -1945,11 +1957,11 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>119.0163803100586</v>
+        <v>119.0163879394531</v>
       </c>
       <c r="C79" t="n">
         <v>169.8200073242188</v>
@@ -1964,11 +1976,11 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>119.3247528076172</v>
+        <v>119.3247985839844</v>
       </c>
       <c r="C80" t="n">
         <v>170.2599945068359</v>
@@ -1983,11 +1995,11 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>124.6624450683594</v>
+        <v>124.6624145507812</v>
       </c>
       <c r="C81" t="n">
         <v>176.3699951171875</v>
@@ -2002,11 +2014,11 @@
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>126.0266342163086</v>
+        <v>126.026611328125</v>
       </c>
       <c r="C82" t="n">
         <v>178.3000030517578</v>
@@ -2021,11 +2033,11 @@
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>134.0703125</v>
+        <v>134.0702667236328</v>
       </c>
       <c r="C83" t="n">
         <v>189.6799926757812</v>
@@ -2040,11 +2052,11 @@
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>140.3387451171875</v>
+        <v>140.3387145996094</v>
       </c>
       <c r="C84" t="n">
         <v>197.0399932861328</v>
@@ -2059,7 +2071,7 @@
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2078,11 +2090,11 @@
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>168.2868041992188</v>
+        <v>168.2868804931641</v>
       </c>
       <c r="C86" t="n">
         <v>236.2799987792969</v>
@@ -2097,11 +2109,11 @@
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>170.7583160400391</v>
+        <v>170.7582550048828</v>
       </c>
       <c r="C87" t="n">
         <v>239.75</v>
@@ -2116,11 +2128,11 @@
       <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>184.2418365478516</v>
+        <v>184.2417907714844</v>
       </c>
       <c r="C88" t="n">
         <v>256.8800048828125</v>
@@ -2135,7 +2147,7 @@
       <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2154,11 +2166,11 @@
       <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>200.2503051757812</v>
+        <v>200.2502899169922</v>
       </c>
       <c r="C90" t="n">
         <v>279.2000122070312</v>
@@ -2173,11 +2185,11 @@
       <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>185.3868408203125</v>
+        <v>185.3868255615234</v>
       </c>
       <c r="C91" t="n">
         <v>256.8500061035156</v>
@@ -2192,11 +2204,11 @@
       <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>203.5105743408203</v>
+        <v>203.5104827880859</v>
       </c>
       <c r="C92" t="n">
         <v>281.9599914550781</v>
@@ -2211,11 +2223,11 @@
       <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>189.1160736083984</v>
+        <v>189.1160278320312</v>
       </c>
       <c r="C93" t="n">
         <v>260.3200073242188</v>
@@ -2230,7 +2242,7 @@
       <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2249,11 +2261,11 @@
       <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>218.531005859375</v>
+        <v>218.5310211181641</v>
       </c>
       <c r="C95" t="n">
         <v>300.8099975585938</v>
@@ -2268,11 +2280,11 @@
       <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>221.1482086181641</v>
+        <v>221.1481475830078</v>
       </c>
       <c r="C96" t="n">
         <v>302.75</v>
@@ -2287,11 +2299,11 @@
       <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>231.1701812744141</v>
+        <v>231.1701507568359</v>
       </c>
       <c r="C97" t="n">
         <v>316.4700012207031</v>
@@ -2306,11 +2318,11 @@
       <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>219.4827117919922</v>
+        <v>219.4826812744141</v>
       </c>
       <c r="C98" t="n">
         <v>300.4700012207031</v>
@@ -2325,11 +2337,11 @@
       <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>222.6748352050781</v>
+        <v>222.6748809814453</v>
       </c>
       <c r="C99" t="n">
         <v>304.8399963378906</v>
@@ -2344,11 +2356,11 @@
       <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>231.1688079833984</v>
+        <v>231.1688385009766</v>
       </c>
       <c r="C100" t="n">
         <v>314.4800109863281</v>
@@ -2363,11 +2375,11 @@
       <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>221.2599487304688</v>
+        <v>221.2598266601562</v>
       </c>
       <c r="C101" t="n">
         <v>301</v>
@@ -2382,11 +2394,11 @@
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>224.126708984375</v>
+        <v>224.1267395019531</v>
       </c>
       <c r="C102" t="n">
         <v>304.8999938964844</v>
@@ -2401,7 +2413,7 @@
       <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2420,11 +2432,11 @@
       <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>225.4017028808594</v>
+        <v>225.4016418457031</v>
       </c>
       <c r="C104" t="n">
         <v>304.7300109863281</v>
@@ -2439,11 +2451,11 @@
       <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>245.9081878662109</v>
+        <v>245.9083251953125</v>
       </c>
       <c r="C105" t="n">
         <v>330.5299987792969</v>
@@ -2458,11 +2470,11 @@
       <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>244.2639617919922</v>
+        <v>244.2639923095703</v>
       </c>
       <c r="C106" t="n">
         <v>328.3200073242188</v>
@@ -2477,11 +2489,11 @@
       <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>253.7794647216797</v>
+        <v>253.7795562744141</v>
       </c>
       <c r="C107" t="n">
         <v>341.1099853515625</v>
@@ -2496,11 +2508,11 @@
       <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>267.1488647460938</v>
+        <v>267.1488342285156</v>
       </c>
       <c r="C108" t="n">
         <v>359.0799865722656</v>
@@ -2515,11 +2527,11 @@
       <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>267.45556640625</v>
+        <v>267.4555358886719</v>
       </c>
       <c r="C109" t="n">
         <v>357.5599975585938</v>
@@ -2534,7 +2546,7 @@
       <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -2553,7 +2565,7 @@
       <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -2572,11 +2584,11 @@
       <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>275.2549743652344</v>
+        <v>275.2549133300781</v>
       </c>
       <c r="C112" t="n">
         <v>365.8399963378906</v>
@@ -2591,11 +2603,11 @@
       <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>273.8253479003906</v>
+        <v>273.8253173828125</v>
       </c>
       <c r="C113" t="n">
         <v>363.9400024414062</v>
@@ -2610,7 +2622,7 @@
       <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -2629,11 +2641,11 @@
       <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>261.9078979492188</v>
+        <v>261.9080505371094</v>
       </c>
       <c r="C115" t="n">
         <v>345.9800109863281</v>
@@ -2648,11 +2660,11 @@
       <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>254.5953979492188</v>
+        <v>254.5953674316406</v>
       </c>
       <c r="C116" t="n">
         <v>336.3200073242188</v>
@@ -2667,11 +2679,11 @@
       <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>230.5859375</v>
+        <v>230.5858459472656</v>
       </c>
       <c r="C117" t="n">
         <v>302.4700012207031</v>
@@ -2686,11 +2698,11 @@
       <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>226.7742309570312</v>
+        <v>226.7742156982422</v>
       </c>
       <c r="C118" t="n">
         <v>297.4700012207031</v>
@@ -2705,11 +2717,11 @@
       <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>268.3220520019531</v>
+        <v>268.3219909667969</v>
       </c>
       <c r="C119" t="n">
         <v>351.9700012207031</v>
@@ -2724,11 +2736,11 @@
       <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>277.2794189453125</v>
+        <v>277.2793579101562</v>
       </c>
       <c r="C120" t="n">
         <v>363.7200012207031</v>
@@ -2743,11 +2755,11 @@
       <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>261.1582641601562</v>
+        <v>261.1583251953125</v>
       </c>
       <c r="C121" t="n">
         <v>340.5199890136719</v>
@@ -2762,11 +2774,11 @@
       <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>241.0185241699219</v>
+        <v>241.0184631347656</v>
       </c>
       <c r="C122" t="n">
         <v>314.260009765625</v>
@@ -2781,11 +2793,11 @@
       <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>239.2545623779297</v>
+        <v>239.2545471191406</v>
       </c>
       <c r="C123" t="n">
         <v>311.9599914550781</v>
@@ -2800,7 +2812,7 @@
       <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -2819,11 +2831,11 @@
       <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>275.2125549316406</v>
+        <v>275.2125244140625</v>
       </c>
       <c r="C125" t="n">
         <v>356.3299865722656</v>
@@ -2838,11 +2850,11 @@
       <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>281.0207214355469</v>
+        <v>281.0206604003906</v>
       </c>
       <c r="C126" t="n">
         <v>363.8500061035156</v>
@@ -2857,11 +2869,11 @@
       <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>266.226318359375</v>
+        <v>266.2262878417969</v>
       </c>
       <c r="C127" t="n">
         <v>342.5299987792969</v>
@@ -2876,11 +2888,11 @@
       <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>284.6622924804688</v>
+        <v>284.6623229980469</v>
       </c>
       <c r="C128" t="n">
         <v>366.25</v>
@@ -2895,11 +2907,11 @@
       <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>291.5365295410156</v>
+        <v>291.53662109375</v>
       </c>
       <c r="C129" t="n">
         <v>372.8099975585938</v>
@@ -2914,11 +2926,11 @@
       <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>283.4429016113281</v>
+        <v>283.4428405761719</v>
       </c>
       <c r="C130" t="n">
         <v>362.4599914550781</v>
@@ -2933,7 +2945,7 @@
       <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -2952,7 +2964,7 @@
       <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -2971,11 +2983,11 @@
       <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>299.3865356445312</v>
+        <v>299.386474609375</v>
       </c>
       <c r="C133" t="n">
         <v>380.5400085449219</v>
@@ -2990,7 +3002,7 @@
       <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3009,11 +3021,11 @@
       <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>304.8307495117188</v>
+        <v>304.8306274414062</v>
       </c>
       <c r="C135" t="n">
         <v>387.4599914550781</v>
@@ -3028,7 +3040,7 @@
       <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3047,11 +3059,11 @@
       <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>304.470458984375</v>
+        <v>304.4704895019531</v>
       </c>
       <c r="C137" t="n">
         <v>384.5700073242188</v>
@@ -3066,11 +3078,11 @@
       <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>324.002197265625</v>
+        <v>324.0021667480469</v>
       </c>
       <c r="C138" t="n">
         <v>409.239990234375</v>
@@ -3085,11 +3097,11 @@
       <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>336.4844970703125</v>
+        <v>336.4845886230469</v>
       </c>
       <c r="C139" t="n">
         <v>422.4100036621094</v>
@@ -3104,11 +3116,11 @@
       <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>339.7665100097656</v>
+        <v>339.7664794921875</v>
       </c>
       <c r="C140" t="n">
         <v>426.5299987792969</v>
@@ -3123,11 +3135,11 @@
       <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>335.7931213378906</v>
+        <v>335.7931823730469</v>
       </c>
       <c r="C141" t="n">
         <v>419.010009765625</v>
@@ -3142,7 +3154,7 @@
       <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3161,11 +3173,11 @@
       <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>377.3215942382812</v>
+        <v>377.3216247558594</v>
       </c>
       <c r="C143" t="n">
         <v>470.8299865722656</v>
@@ -3180,11 +3192,11 @@
       <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>401.6519775390625</v>
+        <v>401.6520690917969</v>
       </c>
       <c r="C144" t="n">
         <v>501.1900024414062</v>
@@ -3199,11 +3211,11 @@
       <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>413.7494201660156</v>
+        <v>413.7493591308594</v>
       </c>
       <c r="C145" t="n">
         <v>513.7100219726562</v>
@@ -3218,11 +3230,11 @@
       <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>452.4817199707031</v>
+        <v>452.4816589355469</v>
       </c>
       <c r="C146" t="n">
         <v>561.7999877929688</v>
@@ -3237,11 +3249,11 @@
       <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>442.5187072753906</v>
+        <v>442.5186157226562</v>
       </c>
       <c r="C147" t="n">
         <v>549.4299926757812</v>
@@ -3256,11 +3268,11 @@
       <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>438.6257629394531</v>
+        <v>438.6256408691406</v>
       </c>
       <c r="C148" t="n">
         <v>541.719970703125</v>
@@ -3275,11 +3287,11 @@
       <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>422.2537231445312</v>
+        <v>422.2537536621094</v>
       </c>
       <c r="C149" t="n">
         <v>521.5</v>
@@ -3294,11 +3306,11 @@
       <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>432.5610961914062</v>
+        <v>432.5610656738281</v>
       </c>
       <c r="C150" t="n">
         <v>534.22998046875</v>
@@ -3313,11 +3325,11 @@
       <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>406.2576599121094</v>
+        <v>406.2576293945312</v>
       </c>
       <c r="C151" t="n">
         <v>499.0400085449219</v>
@@ -3332,11 +3344,11 @@
       <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>409.2859802246094</v>
+        <v>409.2860107421875</v>
       </c>
       <c r="C152" t="n">
         <v>502.760009765625</v>
@@ -3351,7 +3363,7 @@
       <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -3370,11 +3382,11 @@
       <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>386.2273254394531</v>
+        <v>386.2273559570312</v>
       </c>
       <c r="C154" t="n">
         <v>471.3299865722656</v>
@@ -3389,11 +3401,11 @@
       <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>337.1345520019531</v>
+        <v>337.1346130371094</v>
       </c>
       <c r="C155" t="n">
         <v>411.4200134277344</v>
@@ -3408,11 +3420,11 @@
       <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>350.7292175292969</v>
+        <v>350.7291564941406</v>
       </c>
       <c r="C156" t="n">
         <v>428.010009765625</v>
@@ -3427,11 +3439,11 @@
       <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>324.3768310546875</v>
+        <v>324.3768615722656</v>
       </c>
       <c r="C157" t="n">
         <v>392.8200073242188</v>
@@ -3446,11 +3458,11 @@
       <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>342.7584228515625</v>
+        <v>342.7583312988281</v>
       </c>
       <c r="C158" t="n">
         <v>415.0799865722656</v>
@@ -3465,11 +3477,11 @@
       <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>365.9954223632812</v>
+        <v>365.9954528808594</v>
       </c>
       <c r="C159" t="n">
         <v>443.2200012207031</v>
@@ -3484,11 +3496,11 @@
       <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>355.5901794433594</v>
+        <v>355.5903015136719</v>
       </c>
       <c r="C160" t="n">
         <v>427.3699951171875</v>
@@ -3503,7 +3515,7 @@
       <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -3522,11 +3534,11 @@
       <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>345.7637634277344</v>
+        <v>345.7638244628906</v>
       </c>
       <c r="C162" t="n">
         <v>415.5599975585938</v>
@@ -3541,11 +3553,11 @@
       <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>393.4659118652344</v>
+        <v>393.4659423828125</v>
       </c>
       <c r="C163" t="n">
         <v>469.2999877929688</v>
@@ -3560,11 +3572,11 @@
       <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>392.107666015625</v>
+        <v>392.1077270507812</v>
       </c>
       <c r="C164" t="n">
         <v>467.6799926757812</v>
@@ -3579,11 +3591,11 @@
       <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>354.2786560058594</v>
+        <v>354.2785949707031</v>
       </c>
       <c r="C165" t="n">
         <v>422.5599975585938</v>
@@ -3598,11 +3610,11 @@
       <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>376.6180114746094</v>
+        <v>376.6181335449219</v>
       </c>
       <c r="C166" t="n">
         <v>445.6400146484375</v>
@@ -3617,11 +3629,11 @@
       <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>390.1905822753906</v>
+        <v>390.1906127929688</v>
       </c>
       <c r="C167" t="n">
         <v>461.7000122070312</v>
@@ -3636,11 +3648,11 @@
       <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>418.2569885253906</v>
+        <v>418.2569580078125</v>
       </c>
       <c r="C168" t="n">
         <v>494.9100036621094</v>
@@ -3655,11 +3667,11 @@
       <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>427.7406921386719</v>
+        <v>427.7407531738281</v>
       </c>
       <c r="C169" t="n">
         <v>502.7000122070312</v>
@@ -3674,7 +3686,7 @@
       <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -3693,11 +3705,11 @@
       <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>393.9689331054688</v>
+        <v>393.9690246582031</v>
       </c>
       <c r="C171" t="n">
         <v>463.010009765625</v>
@@ -3712,11 +3724,11 @@
       <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>377.2049865722656</v>
+        <v>377.2049560546875</v>
       </c>
       <c r="C172" t="n">
         <v>439.9700012207031</v>
@@ -3731,11 +3743,11 @@
       <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>430.4202270507812</v>
+        <v>430.4202575683594</v>
       </c>
       <c r="C173" t="n">
         <v>502.0400085449219</v>
@@ -3750,11 +3762,11 @@
       <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>453.2256164550781</v>
+        <v>453.2255249023438</v>
       </c>
       <c r="C174" t="n">
         <v>528.6400146484375</v>
@@ -3769,11 +3781,11 @@
       <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>469.5836791992188</v>
+        <v>469.5836486816406</v>
       </c>
       <c r="C175" t="n">
         <v>544.0900268554688</v>
@@ -3788,11 +3800,11 @@
       <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>496.2696228027344</v>
+        <v>496.2695922851562</v>
       </c>
       <c r="C176" t="n">
         <v>575.010009765625</v>
@@ -3807,11 +3819,11 @@
       <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>512.8230590820312</v>
+        <v>512.8231811523438</v>
       </c>
       <c r="C177" t="n">
         <v>594.1900024414062</v>
@@ -3826,11 +3838,11 @@
       <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>489.3002624511719</v>
+        <v>489.3003234863281</v>
       </c>
       <c r="C178" t="n">
         <v>563.5499877929688</v>
@@ -3845,11 +3857,11 @@
       <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>520.2619018554688</v>
+        <v>520.261962890625</v>
       </c>
       <c r="C179" t="n">
         <v>599.2100219726562</v>
@@ -3864,11 +3876,11 @@
       <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>606.3397827148438</v>
+        <v>606.3399047851562</v>
       </c>
       <c r="C180" t="n">
         <v>698.3499755859375</v>
@@ -3883,7 +3895,7 @@
       <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -3902,11 +3914,11 @@
       <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>611.958740234375</v>
+        <v>611.9588012695312</v>
       </c>
       <c r="C182" t="n">
         <v>701.260009765625</v>
@@ -3921,11 +3933,11 @@
       <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>606.0595703125</v>
+        <v>606.0596313476562</v>
       </c>
       <c r="C183" t="n">
         <v>694.5</v>
@@ -3940,11 +3952,11 @@
       <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>661.8443603515625</v>
+        <v>661.84423828125</v>
       </c>
       <c r="C184" t="n">
         <v>753.9600219726562</v>
@@ -3959,7 +3971,7 @@
       <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -3978,7 +3990,7 @@
       <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -3997,7 +4009,7 @@
       <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -4016,11 +4028,11 @@
       <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>764.781982421875</v>
+        <v>764.7821044921875</v>
       </c>
       <c r="C188" t="n">
         <v>867.1699829101562</v>
@@ -4035,11 +4047,11 @@
       <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>831.9144287109375</v>
+        <v>831.9143676757812</v>
       </c>
       <c r="C189" t="n">
         <v>943.2899780273438</v>
@@ -4054,7 +4066,7 @@
       <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -4073,11 +4085,11 @@
       <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>835.6949462890625</v>
+        <v>835.6947631835938</v>
       </c>
       <c r="C191" t="n">
         <v>943.4600219726562</v>
@@ -4092,11 +4104,11 @@
       <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>801.2823486328125</v>
+        <v>801.282470703125</v>
       </c>
       <c r="C192" t="n">
         <v>904.6099853515625</v>
@@ -4111,11 +4123,11 @@
       <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>814.7223510742188</v>
+        <v>814.72216796875</v>
       </c>
       <c r="C193" t="n">
         <v>915.5599975585938</v>
@@ -4130,11 +4142,11 @@
       <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>732.3031616210938</v>
+        <v>732.302978515625</v>
       </c>
       <c r="C194" t="n">
         <v>822.9400024414062</v>
@@ -4149,11 +4161,11 @@
       <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>661.9595336914062</v>
+        <v>661.95947265625</v>
       </c>
       <c r="C195" t="n">
         <v>743.8900146484375</v>
@@ -4168,11 +4180,11 @@
       <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>684.5339965820312</v>
+        <v>684.5341186523438</v>
       </c>
       <c r="C196" t="n">
         <v>764.1699829101562</v>
@@ -4187,7 +4199,7 @@
       <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -4206,11 +4218,11 @@
       <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>599.3536987304688</v>
+        <v>599.353759765625</v>
       </c>
       <c r="C198" t="n">
         <v>669.0800170898438</v>
@@ -4225,11 +4237,11 @@
       <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>549.4766235351562</v>
+        <v>549.4764404296875</v>
       </c>
       <c r="C199" t="n">
         <v>609.0399780273438</v>
@@ -4244,11 +4256,11 @@
       <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>603.7350463867188</v>
+        <v>603.7349243164062</v>
       </c>
       <c r="C200" t="n">
         <v>669.1799926757812</v>
@@ -4263,11 +4275,11 @@
       <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>601.2179565429688</v>
+        <v>601.2178955078125</v>
       </c>
       <c r="C201" t="n">
         <v>666.3900146484375</v>
@@ -4282,11 +4294,11 @@
       <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>500.1724853515625</v>
+        <v>500.17236328125</v>
       </c>
       <c r="C202" t="n">
         <v>550.280029296875</v>
@@ -4301,7 +4313,7 @@
       <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -4320,11 +4332,11 @@
       <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>650.8021240234375</v>
+        <v>650.8021850585938</v>
       </c>
       <c r="C204" t="n">
         <v>716</v>
@@ -4339,11 +4351,11 @@
       <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>648.5436401367188</v>
+        <v>648.5435791015625</v>
       </c>
       <c r="C205" t="n">
         <v>708.6300048828125</v>
@@ -4358,7 +4370,7 @@
       <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -4377,11 +4389,11 @@
       <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>630.9716186523438</v>
+        <v>630.9716796875</v>
       </c>
       <c r="C207" t="n">
         <v>689.4299926757812</v>
@@ -4396,11 +4408,11 @@
       <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>616.81982421875</v>
+        <v>616.8197631835938</v>
       </c>
       <c r="C208" t="n">
         <v>669.1199951171875</v>
@@ -4415,11 +4427,11 @@
       <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>618.7372436523438</v>
+        <v>618.7371826171875</v>
       </c>
       <c r="C209" t="n">
         <v>671.2000122070312</v>
@@ -4434,11 +4446,11 @@
       <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>606.1541137695312</v>
+        <v>606.154052734375</v>
       </c>
       <c r="C210" t="n">
         <v>657.5499877929688</v>
@@ -4453,7 +4465,7 @@
       <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -4472,11 +4484,11 @@
       <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>686.1082763671875</v>
+        <v>686.1082153320312</v>
       </c>
       <c r="C212" t="n">
         <v>738.8499755859375</v>
@@ -4491,7 +4503,7 @@
       <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -4510,7 +4522,7 @@
       <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -4529,11 +4541,11 @@
       <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>572.6983642578125</v>
+        <v>572.6983032226562</v>
       </c>
       <c r="C215" t="n">
         <v>612.280029296875</v>
@@ -4548,7 +4560,7 @@
       <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -4567,11 +4579,11 @@
       <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>764.38671875</v>
+        <v>764.3867797851562</v>
       </c>
       <c r="C217" t="n">
         <v>811.7999877929688</v>
@@ -4586,11 +4598,11 @@
       <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>729.08642578125</v>
+        <v>729.0863647460938</v>
       </c>
       <c r="C218" t="n">
         <v>774.3099975585938</v>
@@ -4605,11 +4617,11 @@
       <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>763.9537353515625</v>
+        <v>763.95361328125</v>
       </c>
       <c r="C219" t="n">
         <v>811.3400268554688</v>
@@ -4624,11 +4636,11 @@
       <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>789.879150390625</v>
+        <v>789.8792114257812</v>
       </c>
       <c r="C220" t="n">
         <v>833.7000122070312</v>
@@ -4643,7 +4655,7 @@
       <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -4662,11 +4674,11 @@
       <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>731.45068359375</v>
+        <v>731.4506225585938</v>
       </c>
       <c r="C222" t="n">
         <v>772.030029296875</v>
@@ -4681,11 +4693,11 @@
       <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>750.8557739257812</v>
+        <v>750.855712890625</v>
       </c>
       <c r="C223" t="n">
         <v>787.3200073242188</v>
@@ -4700,11 +4712,11 @@
       <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>835.9052124023438</v>
+        <v>835.9053955078125</v>
       </c>
       <c r="C224" t="n">
         <v>876.5</v>
@@ -4719,11 +4731,11 @@
       <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>860.0430908203125</v>
+        <v>860.0431518554688</v>
       </c>
       <c r="C225" t="n">
         <v>901.8099975585938</v>
@@ -4738,11 +4750,11 @@
       <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>910.892578125</v>
+        <v>910.8927001953125</v>
       </c>
       <c r="C226" t="n">
         <v>949.510009765625</v>
@@ -4757,11 +4769,11 @@
       <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>941.1306762695312</v>
+        <v>941.1307983398438</v>
       </c>
       <c r="C227" t="n">
         <v>981.030029296875</v>
@@ -4776,7 +4788,7 @@
       <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -4801,11 +4813,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>988.2877197265625</v>
+        <v>988.2877807617188</v>
       </c>
       <c r="C229" t="n">
         <v>1025.109985351562</v>
@@ -4826,11 +4838,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>1036.867919921875</v>
+        <v>1036.86767578125</v>
       </c>
       <c r="C230" t="n">
         <v>1075.5</v>
@@ -4851,7 +4863,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -4876,7 +4888,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -4901,11 +4913,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>886.23095703125</v>
+        <v>886.2310180664062</v>
       </c>
       <c r="C233" t="n">
         <v>914.260009765625</v>
@@ -4926,11 +4938,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>949.8489379882812</v>
+        <v>949.848876953125</v>
       </c>
       <c r="C234" t="n">
         <v>979.8900146484375</v>
@@ -4951,11 +4963,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>1022.468933105469</v>
+        <v>1022.468994140625</v>
       </c>
       <c r="C235" t="n">
         <v>1049.25</v>
@@ -4976,7 +4988,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -5001,11 +5013,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>1098.370727539062</v>
+        <v>1098.370849609375</v>
       </c>
       <c r="C237" t="n">
         <v>1127.140014648438</v>
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>1141.47607421875</v>
+        <v>1141.475952148438</v>
       </c>
       <c r="C238" t="n">
         <v>1165.869995117188</v>
@@ -5051,7 +5063,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -5076,11 +5088,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>1025.387084960938</v>
+        <v>1025.386962890625</v>
       </c>
       <c r="C240" t="n">
         <v>1047.300048828125</v>
@@ -5101,11 +5113,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>1053.045776367188</v>
+        <v>1053.045654296875</v>
       </c>
       <c r="C241" t="n">
         <v>1070.339965820312</v>
@@ -5126,11 +5138,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>1100.8603515625</v>
+        <v>1100.860473632812</v>
       </c>
       <c r="C242" t="n">
         <v>1118.93994140625</v>
@@ -5151,7 +5163,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -5180,7 +5192,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -5209,7 +5221,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -5238,7 +5250,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -5267,7 +5279,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -5296,7 +5308,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -5325,7 +5337,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -5354,32 +5366,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>1060.890014648438</v>
+        <v>1073.449951171875</v>
       </c>
       <c r="C250" t="n">
-        <v>1060.890014648438</v>
+        <v>1073.449951171875</v>
       </c>
       <c r="D250" t="n">
-        <v>8841800</v>
+        <v>9343000</v>
       </c>
       <c r="E250" t="n">
         <v>41.73</v>
       </c>
       <c r="F250" t="n">
-        <v>25.42271782047537</v>
+        <v>25.72369880593997</v>
       </c>
       <c r="G250" t="n">
         <v>154996807</v>
       </c>
       <c r="H250" t="n">
-        <v>164434564848.691</v>
+        <v>166381314905.9465</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05704504609569151</v>
+        <v>0.06027866109525727</v>
       </c>
     </row>
   </sheetData>
@@ -5411,75 +5423,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5515,13 +5527,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5557,13 +5569,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5599,13 +5611,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5641,13 +5653,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5683,13 +5695,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5725,13 +5737,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5767,13 +5779,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5800,7 +5812,7 @@
       <c r="I9" t="n">
         <v>35.31</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K9" t="n">
@@ -5813,13 +5825,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5846,7 +5858,7 @@
       <c r="I10" t="n">
         <v>39.73</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K10" t="n">
@@ -5859,13 +5871,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5892,7 +5904,7 @@
       <c r="I11" t="n">
         <v>41.73</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K11" t="n">
@@ -5929,52 +5941,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C2" t="n">
@@ -6003,10 +6015,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45602</v>
       </c>
       <c r="C3" t="n">
@@ -6035,10 +6047,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C4" t="n">
@@ -6067,10 +6079,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C5" t="n">
@@ -6099,10 +6111,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>45875</v>
       </c>
       <c r="C6" t="n">
@@ -6131,10 +6143,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C7" t="n">
@@ -6163,10 +6175,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C8" t="n">
@@ -6195,10 +6207,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C9" t="n">
@@ -6227,10 +6239,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C10" t="n">
@@ -6277,12 +6289,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BLK.xlsx
+++ b/salidas/empresas/BLK.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>86.82345581054688</v>
+        <v>86.82347106933594</v>
       </c>
       <c r="C3" t="n">
         <v>142.1000061035156</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>85.793212890625</v>
+        <v>85.79318237304688</v>
       </c>
       <c r="C4" t="n">
         <v>140</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>82.11634063720703</v>
+        <v>82.11634826660156</v>
       </c>
       <c r="C6" t="n">
         <v>134</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>85.54867553710938</v>
+        <v>85.54868316650391</v>
       </c>
       <c r="C7" t="n">
         <v>139.1699981689453</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>80.26374053955078</v>
+        <v>80.26375579833984</v>
       </c>
       <c r="C9" t="n">
         <v>130.1499938964844</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>91.88858032226562</v>
+        <v>91.88856506347656</v>
       </c>
       <c r="C10" t="n">
         <v>149</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>88.67408752441406</v>
+        <v>88.67411041259766</v>
       </c>
       <c r="C12" t="n">
         <v>143.3699951171875</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>93.94990539550781</v>
+        <v>93.94993591308594</v>
       </c>
       <c r="C13" t="n">
         <v>151.8999938964844</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>103.7592315673828</v>
+        <v>103.7592391967773</v>
       </c>
       <c r="C14" t="n">
         <v>167.7599945068359</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>97.09526062011719</v>
+        <v>97.09529876708984</v>
       </c>
       <c r="C16" t="n">
         <v>156.3099975585938</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>92.98934173583984</v>
+        <v>92.98934936523438</v>
       </c>
       <c r="C17" t="n">
         <v>149.6999969482422</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>95.3746337890625</v>
+        <v>95.37465667724609</v>
       </c>
       <c r="C18" t="n">
         <v>153.5399932861328</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>97.69725799560547</v>
+        <v>97.69723510742188</v>
       </c>
       <c r="C19" t="n">
         <v>156.5899963378906</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>99.51277160644531</v>
+        <v>99.51280975341797</v>
       </c>
       <c r="C20" t="n">
         <v>159.5</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>97.20075225830078</v>
+        <v>97.2008056640625</v>
       </c>
       <c r="C21" t="n">
         <v>155.1000061035156</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>108.6755905151367</v>
+        <v>108.6756362915039</v>
       </c>
       <c r="C22" t="n">
         <v>173.4100036621094</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>129.6950073242188</v>
+        <v>129.695068359375</v>
       </c>
       <c r="C23" t="n">
         <v>206.9499969482422</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>124.7349090576172</v>
+        <v>124.7349166870117</v>
       </c>
       <c r="C24" t="n">
         <v>198.3699951171875</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>136.32373046875</v>
+        <v>136.3236999511719</v>
       </c>
       <c r="C25" t="n">
         <v>216.8000030517578</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>138.5872955322266</v>
+        <v>138.5873870849609</v>
       </c>
       <c r="C26" t="n">
         <v>220.3999938964844</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>121.5154418945312</v>
+        <v>121.5154647827148</v>
       </c>
       <c r="C27" t="n">
         <v>193.25</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>127.3848571777344</v>
+        <v>127.3847732543945</v>
       </c>
       <c r="C29" t="n">
         <v>201.7899932861328</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>142.0304107666016</v>
+        <v>142.0304412841797</v>
       </c>
       <c r="C30" t="n">
         <v>224.9900054931641</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>112.1445083618164</v>
+        <v>112.1444320678711</v>
       </c>
       <c r="C31" t="n">
         <v>177</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>137.3041076660156</v>
+        <v>137.3040466308594</v>
       </c>
       <c r="C32" t="n">
         <v>216.7100067138672</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>123.6852798461914</v>
+        <v>123.6852035522461</v>
       </c>
       <c r="C34" t="n">
         <v>194.5</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>83.52091979980469</v>
+        <v>83.52094268798828</v>
       </c>
       <c r="C35" t="n">
         <v>131.3399963378906</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>79.94076538085938</v>
+        <v>79.94072723388672</v>
       </c>
       <c r="C36" t="n">
         <v>125.7099990844727</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>85.8404541015625</v>
+        <v>85.84046936035156</v>
       </c>
       <c r="C37" t="n">
         <v>134.1499938964844</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>69.61939239501953</v>
+        <v>69.619384765625</v>
       </c>
       <c r="C38" t="n">
         <v>108.8000030517578</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>61.94718170166016</v>
+        <v>61.94716644287109</v>
       </c>
       <c r="C39" t="n">
         <v>96.80999755859375</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>83.88974761962891</v>
+        <v>83.88972473144531</v>
       </c>
       <c r="C40" t="n">
         <v>130.0399932861328</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>94.5211181640625</v>
+        <v>94.52114868164062</v>
       </c>
       <c r="C41" t="n">
         <v>146.5200042724609</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>102.8946228027344</v>
+        <v>102.8945846557617</v>
       </c>
       <c r="C42" t="n">
         <v>159.5</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>123.5042495727539</v>
+        <v>123.5042266845703</v>
       </c>
       <c r="C44" t="n">
         <v>190.5399932861328</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>129.8598785400391</v>
+        <v>129.8598327636719</v>
       </c>
       <c r="C45" t="n">
         <v>199.5700073242188</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>141.0843963623047</v>
+        <v>141.0844116210938</v>
       </c>
       <c r="C46" t="n">
         <v>216.8200073242188</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>140.8696899414062</v>
+        <v>140.86962890625</v>
       </c>
       <c r="C47" t="n">
         <v>216.4900054931641</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2669067382812</v>
+        <v>148.2669525146484</v>
       </c>
       <c r="C48" t="n">
         <v>227.0800018310547</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>151.6098937988281</v>
+        <v>151.6099090576172</v>
       </c>
       <c r="C49" t="n">
         <v>232.1999969482422</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>142.8606872558594</v>
+        <v>142.8607177734375</v>
       </c>
       <c r="C51" t="n">
         <v>218.8000030517578</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>142.8426818847656</v>
+        <v>142.8427429199219</v>
       </c>
       <c r="C52" t="n">
         <v>217.7599945068359</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>120.697395324707</v>
+        <v>120.6974105834961</v>
       </c>
       <c r="C53" t="n">
         <v>184</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>110.1232147216797</v>
+        <v>110.1232299804688</v>
       </c>
       <c r="C54" t="n">
         <v>167.8800048828125</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>94.63957977294922</v>
+        <v>94.63961791992188</v>
       </c>
       <c r="C55" t="n">
         <v>143.3999938964844</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>103.938606262207</v>
+        <v>103.938591003418</v>
       </c>
       <c r="C56" t="n">
         <v>157.4900054931641</v>
@@ -1543,7 +1543,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>94.34628295898438</v>
+        <v>94.34630584716797</v>
       </c>
       <c r="C57" t="n">
         <v>141.9499969482422</v>
@@ -1562,7 +1562,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>113.1557006835938</v>
+        <v>113.1556854248047</v>
       </c>
       <c r="C58" t="n">
         <v>170.25</v>
@@ -1581,7 +1581,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>113.6475067138672</v>
+        <v>113.6476058959961</v>
       </c>
       <c r="C59" t="n">
         <v>170.9900054931641</v>
@@ -1600,7 +1600,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>108.3370208740234</v>
+        <v>108.3370590209961</v>
       </c>
       <c r="C60" t="n">
         <v>163</v>
@@ -1619,7 +1619,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>127.4498596191406</v>
+        <v>127.4497909545898</v>
       </c>
       <c r="C61" t="n">
         <v>190.5800018310547</v>
@@ -1638,7 +1638,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>132.42529296875</v>
+        <v>132.4253540039062</v>
       </c>
       <c r="C62" t="n">
         <v>198.0200042724609</v>
@@ -1657,7 +1657,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>136.4177703857422</v>
+        <v>136.417724609375</v>
       </c>
       <c r="C63" t="n">
         <v>203.9900054931641</v>
@@ -1676,7 +1676,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>135.3608703613281</v>
+        <v>135.36083984375</v>
       </c>
       <c r="C64" t="n">
         <v>201.0099945068359</v>
@@ -1695,7 +1695,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>131.9466705322266</v>
+        <v>131.9466857910156</v>
       </c>
       <c r="C65" t="n">
         <v>195.9400024414062</v>
@@ -1714,7 +1714,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>138.4247894287109</v>
+        <v>138.4248809814453</v>
       </c>
       <c r="C66" t="n">
         <v>205.5599975585938</v>
@@ -1752,7 +1752,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>121.0093078613281</v>
+        <v>121.0093231201172</v>
       </c>
       <c r="C68" t="n">
         <v>178.4600067138672</v>
@@ -1790,7 +1790,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>101.1951065063477</v>
+        <v>101.1950759887695</v>
       </c>
       <c r="C70" t="n">
         <v>148.0099945068359</v>
@@ -1809,7 +1809,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>107.881721496582</v>
+        <v>107.8817291259766</v>
       </c>
       <c r="C71" t="n">
         <v>157.7899932861328</v>
@@ -1828,7 +1828,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>117.6244659423828</v>
+        <v>117.6244964599609</v>
       </c>
       <c r="C72" t="n">
         <v>172.0399932861328</v>
@@ -1847,7 +1847,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>122.8453140258789</v>
+        <v>122.8453216552734</v>
       </c>
       <c r="C73" t="n">
         <v>178.2400054931641</v>
@@ -1866,7 +1866,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>125.4367294311523</v>
+        <v>125.4367828369141</v>
       </c>
       <c r="C74" t="n">
         <v>182</v>
@@ -1885,7 +1885,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>137.1533508300781</v>
+        <v>137.1533660888672</v>
       </c>
       <c r="C75" t="n">
         <v>199</v>
@@ -1904,7 +1904,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>142.2963256835938</v>
+        <v>142.2962951660156</v>
       </c>
       <c r="C76" t="n">
         <v>204.8999938964844</v>
@@ -1923,7 +1923,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>133.0460510253906</v>
+        <v>133.0460662841797</v>
       </c>
       <c r="C77" t="n">
         <v>191.5800018310547</v>
@@ -1942,7 +1942,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>118.6150283813477</v>
+        <v>118.6150512695312</v>
       </c>
       <c r="C78" t="n">
         <v>170.8000030517578</v>
@@ -1961,7 +1961,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>119.0163879394531</v>
+        <v>119.0164031982422</v>
       </c>
       <c r="C79" t="n">
         <v>169.8200073242188</v>
@@ -1999,7 +1999,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>124.6624145507812</v>
+        <v>124.6624755859375</v>
       </c>
       <c r="C81" t="n">
         <v>176.3699951171875</v>
@@ -2018,7 +2018,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>126.026611328125</v>
+        <v>126.0265655517578</v>
       </c>
       <c r="C82" t="n">
         <v>178.3000030517578</v>
@@ -2037,7 +2037,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>134.0702667236328</v>
+        <v>134.0702972412109</v>
       </c>
       <c r="C83" t="n">
         <v>189.6799926757812</v>
@@ -2056,7 +2056,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>140.3387145996094</v>
+        <v>140.3387298583984</v>
       </c>
       <c r="C84" t="n">
         <v>197.0399932861328</v>
@@ -2075,7 +2075,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>147.2260437011719</v>
+        <v>147.2260284423828</v>
       </c>
       <c r="C85" t="n">
         <v>206.7100067138672</v>
@@ -2094,7 +2094,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>168.2868804931641</v>
+        <v>168.2868194580078</v>
       </c>
       <c r="C86" t="n">
         <v>236.2799987792969</v>
@@ -2113,7 +2113,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>170.7582550048828</v>
+        <v>170.75830078125</v>
       </c>
       <c r="C87" t="n">
         <v>239.75</v>
@@ -2132,7 +2132,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>184.2417907714844</v>
+        <v>184.2417602539062</v>
       </c>
       <c r="C88" t="n">
         <v>256.8800048828125</v>
@@ -2151,7 +2151,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>191.1414947509766</v>
+        <v>191.1415100097656</v>
       </c>
       <c r="C89" t="n">
         <v>266.5</v>
@@ -2189,7 +2189,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>185.3868255615234</v>
+        <v>185.3868408203125</v>
       </c>
       <c r="C91" t="n">
         <v>256.8500061035156</v>
@@ -2208,7 +2208,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>203.5104827880859</v>
+        <v>203.5105285644531</v>
       </c>
       <c r="C92" t="n">
         <v>281.9599914550781</v>
@@ -2227,7 +2227,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>189.1160278320312</v>
+        <v>189.1160125732422</v>
       </c>
       <c r="C93" t="n">
         <v>260.3200073242188</v>
@@ -2246,7 +2246,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>196.5987243652344</v>
+        <v>196.5987091064453</v>
       </c>
       <c r="C94" t="n">
         <v>270.6199951171875</v>
@@ -2265,7 +2265,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>218.5310211181641</v>
+        <v>218.5310974121094</v>
       </c>
       <c r="C95" t="n">
         <v>300.8099975585938</v>
@@ -2284,7 +2284,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>221.1481475830078</v>
+        <v>221.1481628417969</v>
       </c>
       <c r="C96" t="n">
         <v>302.75</v>
@@ -2303,7 +2303,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>231.1701507568359</v>
+        <v>231.1702117919922</v>
       </c>
       <c r="C97" t="n">
         <v>316.4700012207031</v>
@@ -2322,7 +2322,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>219.4826812744141</v>
+        <v>219.4827880859375</v>
       </c>
       <c r="C98" t="n">
         <v>300.4700012207031</v>
@@ -2341,7 +2341,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>222.6748809814453</v>
+        <v>222.6749572753906</v>
       </c>
       <c r="C99" t="n">
         <v>304.8399963378906</v>
@@ -2360,7 +2360,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>231.1688385009766</v>
+        <v>231.1687774658203</v>
       </c>
       <c r="C100" t="n">
         <v>314.4800109863281</v>
@@ -2379,7 +2379,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>221.2598266601562</v>
+        <v>221.2598571777344</v>
       </c>
       <c r="C101" t="n">
         <v>301</v>
@@ -2398,7 +2398,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>224.1267395019531</v>
+        <v>224.1266632080078</v>
       </c>
       <c r="C102" t="n">
         <v>304.8999938964844</v>
@@ -2417,7 +2417,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>236.4006652832031</v>
+        <v>236.4006958007812</v>
       </c>
       <c r="C103" t="n">
         <v>319.6000061035156</v>
@@ -2436,7 +2436,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>225.4016418457031</v>
+        <v>225.4016571044922</v>
       </c>
       <c r="C104" t="n">
         <v>304.7300109863281</v>
@@ -2455,7 +2455,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>245.9083251953125</v>
+        <v>245.9082183837891</v>
       </c>
       <c r="C105" t="n">
         <v>330.5299987792969</v>
@@ -2493,7 +2493,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>253.7795562744141</v>
+        <v>253.7795104980469</v>
       </c>
       <c r="C107" t="n">
         <v>341.1099853515625</v>
@@ -2512,7 +2512,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>267.1488342285156</v>
+        <v>267.1488647460938</v>
       </c>
       <c r="C108" t="n">
         <v>359.0799865722656</v>
@@ -2531,7 +2531,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>267.4555358886719</v>
+        <v>267.4555053710938</v>
       </c>
       <c r="C109" t="n">
         <v>357.5599975585938</v>
@@ -2550,7 +2550,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>254.7021179199219</v>
+        <v>254.7021331787109</v>
       </c>
       <c r="C110" t="n">
         <v>340.510009765625</v>
@@ -2569,7 +2569,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>277.8228454589844</v>
+        <v>277.8228149414062</v>
       </c>
       <c r="C111" t="n">
         <v>371.4200134277344</v>
@@ -2588,7 +2588,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>275.2549133300781</v>
+        <v>275.2549743652344</v>
       </c>
       <c r="C112" t="n">
         <v>365.8399963378906</v>
@@ -2607,7 +2607,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>273.8253173828125</v>
+        <v>273.8253479003906</v>
       </c>
       <c r="C113" t="n">
         <v>363.9400024414062</v>
@@ -2626,7 +2626,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>275.2097473144531</v>
+        <v>275.2097778320312</v>
       </c>
       <c r="C114" t="n">
         <v>365.7799987792969</v>
@@ -2664,7 +2664,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>254.5953674316406</v>
+        <v>254.5953369140625</v>
       </c>
       <c r="C116" t="n">
         <v>336.3200073242188</v>
@@ -2683,7 +2683,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>230.5858459472656</v>
+        <v>230.5860595703125</v>
       </c>
       <c r="C117" t="n">
         <v>302.4700012207031</v>
@@ -2702,7 +2702,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>226.7742156982422</v>
+        <v>226.7742614746094</v>
       </c>
       <c r="C118" t="n">
         <v>297.4700012207031</v>
@@ -2721,7 +2721,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>268.3219909667969</v>
+        <v>268.3218994140625</v>
       </c>
       <c r="C119" t="n">
         <v>351.9700012207031</v>
@@ -2740,7 +2740,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>277.2793579101562</v>
+        <v>277.2795104980469</v>
       </c>
       <c r="C120" t="n">
         <v>363.7200012207031</v>
@@ -2759,7 +2759,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>261.1583251953125</v>
+        <v>261.1584167480469</v>
       </c>
       <c r="C121" t="n">
         <v>340.5199890136719</v>
@@ -2778,7 +2778,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>241.0184631347656</v>
+        <v>241.0186004638672</v>
       </c>
       <c r="C122" t="n">
         <v>314.260009765625</v>
@@ -2797,7 +2797,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>239.2545471191406</v>
+        <v>239.2545166015625</v>
       </c>
       <c r="C123" t="n">
         <v>311.9599914550781</v>
@@ -2816,7 +2816,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>263.0403137207031</v>
+        <v>263.040283203125</v>
       </c>
       <c r="C124" t="n">
         <v>340.5700073242188</v>
@@ -2854,7 +2854,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>281.0206604003906</v>
+        <v>281.0208129882812</v>
       </c>
       <c r="C126" t="n">
         <v>363.8500061035156</v>
@@ -2911,7 +2911,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>291.53662109375</v>
+        <v>291.5364685058594</v>
       </c>
       <c r="C129" t="n">
         <v>372.8099975585938</v>
@@ -2930,7 +2930,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>283.4428405761719</v>
+        <v>283.4429016113281</v>
       </c>
       <c r="C130" t="n">
         <v>362.4599914550781</v>
@@ -2968,7 +2968,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>289.9569702148438</v>
+        <v>289.9569396972656</v>
       </c>
       <c r="C132" t="n">
         <v>370.7900085449219</v>
@@ -3006,7 +3006,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>294.2255249023438</v>
+        <v>294.2254943847656</v>
       </c>
       <c r="C134" t="n">
         <v>373.9800109863281</v>
@@ -3025,7 +3025,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>304.8306274414062</v>
+        <v>304.8306884765625</v>
       </c>
       <c r="C135" t="n">
         <v>387.4599914550781</v>
@@ -3044,7 +3044,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>303.6312866210938</v>
+        <v>303.6312255859375</v>
       </c>
       <c r="C136" t="n">
         <v>383.510009765625</v>
@@ -3082,7 +3082,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>324.0021667480469</v>
+        <v>324.0020446777344</v>
       </c>
       <c r="C138" t="n">
         <v>409.239990234375</v>
@@ -3101,7 +3101,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>336.4845886230469</v>
+        <v>336.4845275878906</v>
       </c>
       <c r="C139" t="n">
         <v>422.4100036621094</v>
@@ -3120,7 +3120,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>339.7664794921875</v>
+        <v>339.7665100097656</v>
       </c>
       <c r="C140" t="n">
         <v>426.5299987792969</v>
@@ -3139,7 +3139,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>335.7931823730469</v>
+        <v>335.7932434082031</v>
       </c>
       <c r="C141" t="n">
         <v>419.010009765625</v>
@@ -3177,7 +3177,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>377.3216247558594</v>
+        <v>377.3215026855469</v>
       </c>
       <c r="C143" t="n">
         <v>470.8299865722656</v>
@@ -3196,7 +3196,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>401.6520690917969</v>
+        <v>401.6520080566406</v>
       </c>
       <c r="C144" t="n">
         <v>501.1900024414062</v>
@@ -3215,7 +3215,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>413.7493591308594</v>
+        <v>413.7493286132812</v>
       </c>
       <c r="C145" t="n">
         <v>513.7100219726562</v>
@@ -3234,7 +3234,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>452.4816589355469</v>
+        <v>452.4817199707031</v>
       </c>
       <c r="C146" t="n">
         <v>561.7999877929688</v>
@@ -3253,7 +3253,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>442.5186157226562</v>
+        <v>442.5187072753906</v>
       </c>
       <c r="C147" t="n">
         <v>549.4299926757812</v>
@@ -3272,7 +3272,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>438.6256408691406</v>
+        <v>438.6256713867188</v>
       </c>
       <c r="C148" t="n">
         <v>541.719970703125</v>
@@ -3329,7 +3329,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>406.2576293945312</v>
+        <v>406.2576599121094</v>
       </c>
       <c r="C151" t="n">
         <v>499.0400085449219</v>
@@ -3348,7 +3348,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>409.2860107421875</v>
+        <v>409.2860412597656</v>
       </c>
       <c r="C152" t="n">
         <v>502.760009765625</v>
@@ -3367,7 +3367,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>389.9923706054688</v>
+        <v>389.9922790527344</v>
       </c>
       <c r="C153" t="n">
         <v>479.0599975585938</v>
@@ -3386,7 +3386,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>386.2273559570312</v>
+        <v>386.2273254394531</v>
       </c>
       <c r="C154" t="n">
         <v>471.3299865722656</v>
@@ -3405,7 +3405,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>337.1346130371094</v>
+        <v>337.1345520019531</v>
       </c>
       <c r="C155" t="n">
         <v>411.4200134277344</v>
@@ -3424,7 +3424,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>350.7291564941406</v>
+        <v>350.7291259765625</v>
       </c>
       <c r="C156" t="n">
         <v>428.010009765625</v>
@@ -3443,7 +3443,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>324.3768615722656</v>
+        <v>324.3768920898438</v>
       </c>
       <c r="C157" t="n">
         <v>392.8200073242188</v>
@@ -3500,7 +3500,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>355.5903015136719</v>
+        <v>355.5902404785156</v>
       </c>
       <c r="C160" t="n">
         <v>427.3699951171875</v>
@@ -3519,7 +3519,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>403.7405090332031</v>
+        <v>403.7405395507812</v>
       </c>
       <c r="C161" t="n">
         <v>485.239990234375</v>
@@ -3538,7 +3538,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>345.7638244628906</v>
+        <v>345.7637939453125</v>
       </c>
       <c r="C162" t="n">
         <v>415.5599975585938</v>
@@ -3557,7 +3557,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>393.4659423828125</v>
+        <v>393.4659118652344</v>
       </c>
       <c r="C163" t="n">
         <v>469.2999877929688</v>
@@ -3576,7 +3576,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>392.1077270507812</v>
+        <v>392.1076965332031</v>
       </c>
       <c r="C164" t="n">
         <v>467.6799926757812</v>
@@ -3595,7 +3595,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>354.2785949707031</v>
+        <v>354.2786560058594</v>
       </c>
       <c r="C165" t="n">
         <v>422.5599975585938</v>
@@ -3614,7 +3614,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>376.6181335449219</v>
+        <v>376.6180114746094</v>
       </c>
       <c r="C166" t="n">
         <v>445.6400146484375</v>
@@ -3633,7 +3633,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>390.1906127929688</v>
+        <v>390.1906433105469</v>
       </c>
       <c r="C167" t="n">
         <v>461.7000122070312</v>
@@ -3652,7 +3652,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>418.2569580078125</v>
+        <v>418.2569274902344</v>
       </c>
       <c r="C168" t="n">
         <v>494.9100036621094</v>
@@ -3671,7 +3671,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>427.7407531738281</v>
+        <v>427.7406921386719</v>
       </c>
       <c r="C169" t="n">
         <v>502.7000122070312</v>
@@ -3690,7 +3690,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>448.7150573730469</v>
+        <v>448.715087890625</v>
       </c>
       <c r="C170" t="n">
         <v>527.3499755859375</v>
@@ -3709,7 +3709,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>393.9690246582031</v>
+        <v>393.9690551757812</v>
       </c>
       <c r="C171" t="n">
         <v>463.010009765625</v>
@@ -3728,7 +3728,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>377.2049560546875</v>
+        <v>377.2049255371094</v>
       </c>
       <c r="C172" t="n">
         <v>439.9700012207031</v>
@@ -3747,7 +3747,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>430.4202575683594</v>
+        <v>430.4202270507812</v>
       </c>
       <c r="C173" t="n">
         <v>502.0400085449219</v>
@@ -3785,7 +3785,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>469.5836486816406</v>
+        <v>469.5837097167969</v>
       </c>
       <c r="C175" t="n">
         <v>544.0900268554688</v>
@@ -3804,7 +3804,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>496.2695922851562</v>
+        <v>496.2696838378906</v>
       </c>
       <c r="C176" t="n">
         <v>575.010009765625</v>
@@ -3823,7 +3823,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>512.8231811523438</v>
+        <v>512.8230590820312</v>
       </c>
       <c r="C177" t="n">
         <v>594.1900024414062</v>
@@ -3861,7 +3861,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>520.261962890625</v>
+        <v>520.2618408203125</v>
       </c>
       <c r="C179" t="n">
         <v>599.2100219726562</v>
@@ -3880,7 +3880,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>606.3399047851562</v>
+        <v>606.33984375</v>
       </c>
       <c r="C180" t="n">
         <v>698.3499755859375</v>
@@ -3899,7 +3899,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>629.6561889648438</v>
+        <v>629.65625</v>
       </c>
       <c r="C181" t="n">
         <v>721.5399780273438</v>
@@ -3918,7 +3918,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>611.9588012695312</v>
+        <v>611.958740234375</v>
       </c>
       <c r="C182" t="n">
         <v>701.260009765625</v>
@@ -3937,7 +3937,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>606.0596313476562</v>
+        <v>606.0595703125</v>
       </c>
       <c r="C183" t="n">
         <v>694.5</v>
@@ -3956,7 +3956,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>661.84423828125</v>
+        <v>661.8442993164062</v>
       </c>
       <c r="C184" t="n">
         <v>753.9600219726562</v>
@@ -3975,7 +3975,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>719.2012939453125</v>
+        <v>719.2014770507812</v>
       </c>
       <c r="C185" t="n">
         <v>819.2999877929688</v>
@@ -3994,7 +3994,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>769.8869018554688</v>
+        <v>769.8868408203125</v>
       </c>
       <c r="C186" t="n">
         <v>877.0399780273438</v>
@@ -4013,7 +4013,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>771.6609497070312</v>
+        <v>771.6610717773438</v>
       </c>
       <c r="C187" t="n">
         <v>874.969970703125</v>
@@ -4051,7 +4051,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>831.9143676757812</v>
+        <v>831.914306640625</v>
       </c>
       <c r="C189" t="n">
         <v>943.2899780273438</v>
@@ -4070,7 +4070,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>742.8654174804688</v>
+        <v>742.8653564453125</v>
       </c>
       <c r="C190" t="n">
         <v>838.6599731445312</v>
@@ -4089,7 +4089,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>835.6947631835938</v>
+        <v>835.69482421875</v>
       </c>
       <c r="C191" t="n">
         <v>943.4600219726562</v>
@@ -4146,7 +4146,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>732.302978515625</v>
+        <v>732.3031616210938</v>
       </c>
       <c r="C194" t="n">
         <v>822.9400024414062</v>
@@ -4165,7 +4165,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>661.95947265625</v>
+        <v>661.9595947265625</v>
       </c>
       <c r="C195" t="n">
         <v>743.8900146484375</v>
@@ -4203,7 +4203,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>559.5807495117188</v>
+        <v>559.5806884765625</v>
       </c>
       <c r="C197" t="n">
         <v>624.6799926757812</v>
@@ -4222,7 +4222,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>599.353759765625</v>
+        <v>599.3536376953125</v>
       </c>
       <c r="C198" t="n">
         <v>669.0800170898438</v>
@@ -4241,7 +4241,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>549.4764404296875</v>
+        <v>549.4766235351562</v>
       </c>
       <c r="C199" t="n">
         <v>609.0399780273438</v>
@@ -4260,7 +4260,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>603.7349243164062</v>
+        <v>603.7349853515625</v>
       </c>
       <c r="C200" t="n">
         <v>669.1799926757812</v>
@@ -4279,7 +4279,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>601.2178955078125</v>
+        <v>601.2178344726562</v>
       </c>
       <c r="C201" t="n">
         <v>666.3900146484375</v>
@@ -4298,7 +4298,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>500.17236328125</v>
+        <v>500.1725158691406</v>
       </c>
       <c r="C202" t="n">
         <v>550.280029296875</v>
@@ -4317,7 +4317,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>587.094482421875</v>
+        <v>587.0945434570312</v>
       </c>
       <c r="C203" t="n">
         <v>645.9099731445312</v>
@@ -4355,7 +4355,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>648.5435791015625</v>
+        <v>648.5436401367188</v>
       </c>
       <c r="C205" t="n">
         <v>708.6300048828125</v>
@@ -4393,7 +4393,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>630.9716796875</v>
+        <v>630.9716186523438</v>
       </c>
       <c r="C207" t="n">
         <v>689.4299926757812</v>
@@ -4450,7 +4450,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>606.154052734375</v>
+        <v>606.1541137695312</v>
       </c>
       <c r="C210" t="n">
         <v>657.5499877929688</v>
@@ -4488,7 +4488,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>686.1082153320312</v>
+        <v>686.108154296875</v>
       </c>
       <c r="C212" t="n">
         <v>738.8499755859375</v>
@@ -4507,7 +4507,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>650.5328369140625</v>
+        <v>650.532958984375</v>
       </c>
       <c r="C213" t="n">
         <v>700.5399780273438</v>
@@ -4564,7 +4564,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>702.6655883789062</v>
+        <v>702.66552734375</v>
       </c>
       <c r="C216" t="n">
         <v>751.22998046875</v>
@@ -4583,7 +4583,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>764.3867797851562</v>
+        <v>764.3868408203125</v>
       </c>
       <c r="C217" t="n">
         <v>811.7999877929688</v>
@@ -4621,7 +4621,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>763.95361328125</v>
+        <v>763.9536743164062</v>
       </c>
       <c r="C219" t="n">
         <v>811.3400268554688</v>
@@ -4640,7 +4640,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>789.8792114257812</v>
+        <v>789.8792724609375</v>
       </c>
       <c r="C220" t="n">
         <v>833.7000122070312</v>
@@ -4697,7 +4697,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>750.855712890625</v>
+        <v>750.8556518554688</v>
       </c>
       <c r="C223" t="n">
         <v>787.3200073242188</v>
@@ -4716,7 +4716,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>835.9053955078125</v>
+        <v>835.9053344726562</v>
       </c>
       <c r="C224" t="n">
         <v>876.5</v>
@@ -4735,7 +4735,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>860.0431518554688</v>
+        <v>860.0430297851562</v>
       </c>
       <c r="C225" t="n">
         <v>901.8099975585938</v>
@@ -4773,7 +4773,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>941.1307983398438</v>
+        <v>941.1307373046875</v>
       </c>
       <c r="C227" t="n">
         <v>981.030029296875</v>
@@ -4792,7 +4792,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>981.2018432617188</v>
+        <v>981.201904296875</v>
       </c>
       <c r="C228" t="n">
         <v>1022.799987792969</v>
@@ -4817,7 +4817,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>988.2877807617188</v>
+        <v>988.2876586914062</v>
       </c>
       <c r="C229" t="n">
         <v>1025.109985351562</v>
@@ -4892,7 +4892,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>917.463134765625</v>
+        <v>917.4631958007812</v>
       </c>
       <c r="C232" t="n">
         <v>946.47998046875</v>
@@ -4942,7 +4942,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>949.848876953125</v>
+        <v>949.8489379882812</v>
       </c>
       <c r="C234" t="n">
         <v>979.8900146484375</v>
@@ -4967,7 +4967,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>1022.468994140625</v>
+        <v>1022.468872070312</v>
       </c>
       <c r="C235" t="n">
         <v>1049.25</v>
@@ -5067,7 +5067,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>1060.154052734375</v>
+        <v>1060.153930664062</v>
       </c>
       <c r="C239" t="n">
         <v>1082.81005859375</v>
